--- a/IaR_GaR_April_2026/Outputs/wis/wis_skewt_inflation.xlsx
+++ b/IaR_GaR_April_2026/Outputs/wis/wis_skewt_inflation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="8" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="20" uniqueCount="5">
   <si>
     <t>Specification</t>
   </si>
@@ -103,10 +103,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.453125" customWidth="true"/>
+    <col min="1" max="1" width="2.90625" customWidth="true"/>
     <col min="2" max="2" width="76.54296875" customWidth="true"/>
   </cols>
   <sheetData>
@@ -142,6 +142,54 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>1</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>13</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>25</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>1</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>13</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>25</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>